--- a/TestData/LV_TS01_ValidateERPSection.xlsx
+++ b/TestData/LV_TS01_ValidateERPSection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A6CD37-6AA7-4EBA-810A-AC4C5F4C8B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BA8C81-91AA-4C48-B511-FF5319AA9427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -42,9 +42,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -273,9 +270,6 @@
     <t>Dimitri Drone</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>10000</t>
   </si>
   <si>
@@ -328,6 +322,12 @@
   </si>
   <si>
     <t>LegalAdv</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
@@ -660,49 +660,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s">
         <v>77</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>84</v>
       </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>86</v>
-      </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -713,16 +713,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC61769-6521-44E3-AD63-111C325FBA29}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -733,39 +733,39 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7F95D39-759B-42B8-9083-067230CD3FBE}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -776,35 +776,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" customWidth="1"/>
-    <col min="27" max="27" width="11.42578125" customWidth="1"/>
-    <col min="29" max="29" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.33203125" customWidth="1"/>
+    <col min="27" max="27" width="11.44140625" customWidth="1"/>
+    <col min="29" max="29" width="21.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -815,373 +815,373 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="I2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="S1" s="1" t="s">
+      <c r="N2" t="s">
+        <v>69</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="R2" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U1" s="1" t="s">
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="U2" t="s">
         <v>26</v>
       </c>
-      <c r="V1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="V2" t="s">
+        <v>53</v>
+      </c>
+      <c r="W2" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X2" t="s">
         <v>31</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Y2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z2" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AA2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC2" t="s">
         <v>93</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD2" t="s">
         <v>94</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="U3" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" t="s">
         <v>53</v>
       </c>
-      <c r="B2" t="s">
+      <c r="W3" t="s">
+        <v>29</v>
+      </c>
+      <c r="X3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" t="s">
+        <v>95</v>
+      </c>
+      <c r="L4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="R4" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="U4" t="s">
+        <v>26</v>
+      </c>
+      <c r="V4" t="s">
         <v>53</v>
       </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="R2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U2" t="s">
-        <v>27</v>
-      </c>
-      <c r="V2" t="s">
-        <v>54</v>
-      </c>
-      <c r="W2" t="s">
-        <v>30</v>
-      </c>
-      <c r="X2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" t="s">
-        <v>97</v>
-      </c>
-      <c r="L3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N3" t="s">
-        <v>56</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="R3" t="s">
-        <v>24</v>
-      </c>
-      <c r="S3" t="s">
-        <v>24</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U3" t="s">
-        <v>27</v>
-      </c>
-      <c r="V3" t="s">
-        <v>54</v>
-      </c>
-      <c r="W3" t="s">
-        <v>30</v>
-      </c>
-      <c r="X3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y3" t="s">
+      <c r="W4" t="s">
+        <v>29</v>
+      </c>
+      <c r="X4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y4" t="s">
         <v>57</v>
       </c>
-      <c r="Z3" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" t="s">
-        <v>97</v>
-      </c>
-      <c r="L4" t="s">
-        <v>52</v>
-      </c>
-      <c r="M4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="R4" t="s">
-        <v>24</v>
-      </c>
-      <c r="S4" t="s">
-        <v>24</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="U4" t="s">
-        <v>27</v>
-      </c>
-      <c r="V4" t="s">
-        <v>54</v>
-      </c>
-      <c r="W4" t="s">
-        <v>30</v>
-      </c>
-      <c r="X4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>58</v>
-      </c>
       <c r="Z4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AC4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1193,47 +1193,47 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
         <v>65</v>
       </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>66</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>67</v>
-      </c>
-      <c r="E2" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1245,66 +1245,66 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
         <v>40</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" t="s">
-        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1316,28 +1316,28 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TS01_ValidateERPSection.xlsx
+++ b/TestData/LV_TS01_ValidateERPSection.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BA8C81-91AA-4C48-B511-FF5319AA9427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C4E2DA-46B1-48C8-87CC-E7BBED5A20C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -327,7 +327,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -660,14 +660,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -678,7 +678,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -689,7 +689,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>78</v>
       </c>
@@ -697,7 +697,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>84</v>
       </c>
@@ -713,14 +713,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC61769-6521-44E3-AD63-111C325FBA29}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -733,37 +733,37 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7F95D39-759B-42B8-9083-067230CD3FBE}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>89</v>
       </c>
@@ -776,35 +776,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE4"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.6640625" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.33203125" customWidth="1"/>
-    <col min="27" max="27" width="11.44140625" customWidth="1"/>
-    <col min="29" max="29" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" customWidth="1"/>
+    <col min="27" max="27" width="11.42578125" customWidth="1"/>
+    <col min="29" max="29" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -899,7 +899,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -994,7 +994,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -1193,16 +1193,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -1245,17 +1245,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -1316,14 +1316,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>70</v>
       </c>

--- a/TestData/LV_TS01_ValidateERPSection.xlsx
+++ b/TestData/LV_TS01_ValidateERPSection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F042F4-E19D-4CFC-B175-312D21F2498B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462CAC9A-3A77-4D40-ADF5-4AD85654935D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -213,9 +213,6 @@
     <t>Debtor Advisors</t>
   </si>
   <si>
-    <t>Debt Capital Markets</t>
-  </si>
-  <si>
     <t>IG</t>
   </si>
   <si>
@@ -328,6 +325,9 @@
   </si>
   <si>
     <t>BUS - Business Services</t>
+  </si>
+  <si>
+    <t>Debt Financing</t>
   </si>
 </sst>
 </file>
@@ -672,37 +672,37 @@
         <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -717,12 +717,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -740,32 +740,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -815,7 +815,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -890,13 +890,13 @@
         <v>42</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="AE1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -931,7 +931,7 @@
         <v>7</v>
       </c>
       <c r="K2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L2" t="s">
         <v>51</v>
@@ -940,16 +940,16 @@
         <v>15</v>
       </c>
       <c r="N2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R2" t="s">
         <v>23</v>
@@ -958,7 +958,7 @@
         <v>23</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U2" t="s">
         <v>26</v>
@@ -979,19 +979,19 @@
         <v>38</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD2" t="s">
         <v>92</v>
       </c>
-      <c r="AD2" t="s">
-        <v>93</v>
-      </c>
       <c r="AE2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -1005,7 +1005,7 @@
         <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -1026,7 +1026,7 @@
         <v>7</v>
       </c>
       <c r="K3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s">
         <v>51</v>
@@ -1038,13 +1038,13 @@
         <v>55</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R3" t="s">
         <v>23</v>
@@ -1053,7 +1053,7 @@
         <v>23</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U3" t="s">
         <v>26</v>
@@ -1074,19 +1074,19 @@
         <v>38</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD3" t="s">
         <v>92</v>
       </c>
-      <c r="AD3" t="s">
-        <v>93</v>
-      </c>
       <c r="AE3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
@@ -1100,7 +1100,7 @@
         <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -1121,7 +1121,7 @@
         <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L4" t="s">
         <v>51</v>
@@ -1133,13 +1133,13 @@
         <v>58</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R4" t="s">
         <v>23</v>
@@ -1148,7 +1148,7 @@
         <v>23</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U4" t="s">
         <v>26</v>
@@ -1169,10 +1169,10 @@
         <v>38</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AC4" t="s">
         <v>7</v>
@@ -1204,10 +1204,10 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -1221,19 +1221,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" t="s">
         <v>64</v>
       </c>
-      <c r="B2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>65</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>66</v>
-      </c>
-      <c r="E2" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1328,16 +1328,16 @@
         <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
